--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,414 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124754572</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>782121</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7290732</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124754571</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>782209</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7290451</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124754542</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90934</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>782254</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7290430</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124754577</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>782578</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7290125</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754571</v>
+        <v>124754577</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782209</v>
+        <v>782578</v>
       </c>
       <c r="R4" t="n">
-        <v>7290451</v>
+        <v>7290125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754577</v>
+        <v>124754571</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782578</v>
+        <v>782209</v>
       </c>
       <c r="R6" t="n">
-        <v>7290125</v>
+        <v>7290451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1182,521 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124791552</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>782269</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7290338</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124791549</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>782377</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7290562</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124791553</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>782220</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7290373</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124791544</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92277</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>782230</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7290358</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124791540</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>782565</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7290181</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754572</v>
+        <v>124754577</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782121</v>
+        <v>782578</v>
       </c>
       <c r="R3" t="n">
-        <v>7290732</v>
+        <v>7290125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754577</v>
+        <v>124754542</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>90934</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782578</v>
+        <v>782254</v>
       </c>
       <c r="R4" t="n">
-        <v>7290125</v>
+        <v>7290430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754542</v>
+        <v>124754572</v>
       </c>
       <c r="B5" t="n">
-        <v>90934</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782254</v>
+        <v>782121</v>
       </c>
       <c r="R5" t="n">
-        <v>7290430</v>
+        <v>7290732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791552</v>
+        <v>124791549</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782269</v>
+        <v>782377</v>
       </c>
       <c r="R7" t="n">
-        <v>7290338</v>
+        <v>7290562</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791549</v>
+        <v>124791552</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782377</v>
+        <v>782269</v>
       </c>
       <c r="R8" t="n">
-        <v>7290562</v>
+        <v>7290338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791553</v>
+        <v>124791544</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>92277</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782220</v>
+        <v>782230</v>
       </c>
       <c r="R9" t="n">
-        <v>7290373</v>
+        <v>7290358</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791544</v>
+        <v>124791553</v>
       </c>
       <c r="B10" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782230</v>
+        <v>782220</v>
       </c>
       <c r="R10" t="n">
-        <v>7290358</v>
+        <v>7290373</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754577</v>
+        <v>124754571</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782578</v>
+        <v>782209</v>
       </c>
       <c r="R3" t="n">
-        <v>7290125</v>
+        <v>7290451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754542</v>
+        <v>124754574</v>
       </c>
       <c r="B4" t="n">
-        <v>90934</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782254</v>
+        <v>782121</v>
       </c>
       <c r="R4" t="n">
-        <v>7290430</v>
+        <v>7290732</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Silverstubbe delvis nedbruden</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754572</v>
+        <v>124754577</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782121</v>
+        <v>782578</v>
       </c>
       <c r="R5" t="n">
-        <v>7290732</v>
+        <v>7290125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754571</v>
+        <v>124754542</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>90934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782209</v>
+        <v>782254</v>
       </c>
       <c r="R6" t="n">
-        <v>7290451</v>
+        <v>7290430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791549</v>
+        <v>124791544</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>92277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782377</v>
+        <v>782230</v>
       </c>
       <c r="R7" t="n">
-        <v>7290562</v>
+        <v>7290358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791544</v>
+        <v>124791549</v>
       </c>
       <c r="B9" t="n">
-        <v>92277</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6055</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782230</v>
+        <v>782377</v>
       </c>
       <c r="R9" t="n">
-        <v>7290358</v>
+        <v>7290562</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791544</v>
+        <v>124791552</v>
       </c>
       <c r="B7" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782230</v>
+        <v>782269</v>
       </c>
       <c r="R7" t="n">
-        <v>7290358</v>
+        <v>7290338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791552</v>
+        <v>124791544</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>92277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782269</v>
+        <v>782230</v>
       </c>
       <c r="R8" t="n">
-        <v>7290338</v>
+        <v>7290358</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791552</v>
+        <v>124791544</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782269</v>
+        <v>782230</v>
       </c>
       <c r="R7" t="n">
-        <v>7290338</v>
+        <v>7290358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791544</v>
+        <v>124791552</v>
       </c>
       <c r="B8" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782230</v>
+        <v>782269</v>
       </c>
       <c r="R8" t="n">
-        <v>7290358</v>
+        <v>7290338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754571</v>
+        <v>124754577</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782209</v>
+        <v>782578</v>
       </c>
       <c r="R3" t="n">
-        <v>7290451</v>
+        <v>7290125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754574</v>
+        <v>124754572</v>
       </c>
       <c r="B4" t="n">
         <v>78455</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Silverstubbe delvis nedbruden</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754577</v>
+        <v>124754571</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782578</v>
+        <v>782209</v>
       </c>
       <c r="R5" t="n">
-        <v>7290125</v>
+        <v>7290451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791544</v>
+        <v>124791552</v>
       </c>
       <c r="B7" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782230</v>
+        <v>782269</v>
       </c>
       <c r="R7" t="n">
-        <v>7290358</v>
+        <v>7290338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791552</v>
+        <v>124791540</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782269</v>
+        <v>782565</v>
       </c>
       <c r="R8" t="n">
-        <v>7290338</v>
+        <v>7290181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791553</v>
+        <v>124791544</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>92277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782220</v>
+        <v>782230</v>
       </c>
       <c r="R10" t="n">
-        <v>7290373</v>
+        <v>7290358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791540</v>
+        <v>124791553</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782565</v>
+        <v>782220</v>
       </c>
       <c r="R11" t="n">
-        <v>7290181</v>
+        <v>7290373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754577</v>
+        <v>124754542</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>90934</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782578</v>
+        <v>782254</v>
       </c>
       <c r="R3" t="n">
-        <v>7290125</v>
+        <v>7290430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754572</v>
+        <v>124754577</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782121</v>
+        <v>782578</v>
       </c>
       <c r="R4" t="n">
-        <v>7290732</v>
+        <v>7290125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754571</v>
+        <v>124754572</v>
       </c>
       <c r="B5" t="n">
         <v>78455</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782209</v>
+        <v>782121</v>
       </c>
       <c r="R5" t="n">
-        <v>7290451</v>
+        <v>7290732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754542</v>
+        <v>124754571</v>
       </c>
       <c r="B6" t="n">
-        <v>90934</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782254</v>
+        <v>782209</v>
       </c>
       <c r="R6" t="n">
-        <v>7290430</v>
+        <v>7290451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791552</v>
+        <v>124791553</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782269</v>
+        <v>782220</v>
       </c>
       <c r="R7" t="n">
-        <v>7290338</v>
+        <v>7290373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791544</v>
+        <v>124791552</v>
       </c>
       <c r="B10" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782230</v>
+        <v>782269</v>
       </c>
       <c r="R10" t="n">
-        <v>7290358</v>
+        <v>7290338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791553</v>
+        <v>124791544</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>92277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782220</v>
+        <v>782230</v>
       </c>
       <c r="R11" t="n">
-        <v>7290373</v>
+        <v>7290358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754577</v>
+        <v>124754572</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782578</v>
+        <v>782121</v>
       </c>
       <c r="R4" t="n">
-        <v>7290125</v>
+        <v>7290732</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754572</v>
+        <v>124754577</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782121</v>
+        <v>782578</v>
       </c>
       <c r="R5" t="n">
-        <v>7290732</v>
+        <v>7290125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791553</v>
+        <v>124791544</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782220</v>
+        <v>782230</v>
       </c>
       <c r="R7" t="n">
-        <v>7290373</v>
+        <v>7290358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791540</v>
+        <v>124791553</v>
       </c>
       <c r="B8" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782565</v>
+        <v>782220</v>
       </c>
       <c r="R8" t="n">
-        <v>7290181</v>
+        <v>7290373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791544</v>
+        <v>124791540</v>
       </c>
       <c r="B11" t="n">
-        <v>92277</v>
+        <v>79399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782230</v>
+        <v>782565</v>
       </c>
       <c r="R11" t="n">
-        <v>7290358</v>
+        <v>7290181</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1698,6 +1698,1142 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124754557</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>782122</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7290733</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125141672</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>782114</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7290605</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124754564</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92328</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>782219</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7290375</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124754560</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>782118</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7290721</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124754567</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>782118</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7290718</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125141702</v>
+      </c>
+      <c r="B17" t="n">
+        <v>74893</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>308</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>782114</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7290605</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125141688</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>782118</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7290721</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125141675</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92318</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>782232</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7290364</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125141668</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>782209</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7290451</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124754580</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74893</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>308</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>782435</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7290481</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125141670</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>782114</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7290605</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791544</v>
+        <v>124791549</v>
       </c>
       <c r="B7" t="n">
-        <v>92277</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6055</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782230</v>
+        <v>782377</v>
       </c>
       <c r="R7" t="n">
-        <v>7290358</v>
+        <v>7290562</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791553</v>
+        <v>124791540</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782220</v>
+        <v>782565</v>
       </c>
       <c r="R8" t="n">
-        <v>7290373</v>
+        <v>7290181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791549</v>
+        <v>124791552</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782377</v>
+        <v>782269</v>
       </c>
       <c r="R9" t="n">
-        <v>7290562</v>
+        <v>7290338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791552</v>
+        <v>124791553</v>
       </c>
       <c r="B10" t="n">
         <v>92293</v>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782269</v>
+        <v>782220</v>
       </c>
       <c r="R10" t="n">
-        <v>7290338</v>
+        <v>7290373</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791540</v>
+        <v>124791544</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
+        <v>92277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782565</v>
+        <v>782230</v>
       </c>
       <c r="R11" t="n">
-        <v>7290181</v>
+        <v>7290358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124754557</v>
+        <v>125141687</v>
       </c>
       <c r="B12" t="n">
-        <v>96979</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782122</v>
+        <v>782118</v>
       </c>
       <c r="R12" t="n">
-        <v>7290733</v>
+        <v>7290718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125141672</v>
+        <v>124754568</v>
       </c>
       <c r="B13" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R13" t="n">
-        <v>7290605</v>
+        <v>7290721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124754564</v>
+        <v>125141672</v>
       </c>
       <c r="B14" t="n">
-        <v>92328</v>
+        <v>79399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782219</v>
+        <v>782114</v>
       </c>
       <c r="R14" t="n">
-        <v>7290375</v>
+        <v>7290605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754560</v>
+        <v>124754564</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>92328</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782118</v>
+        <v>782219</v>
       </c>
       <c r="R15" t="n">
-        <v>7290721</v>
+        <v>7290375</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124754567</v>
+        <v>125141670</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R16" t="n">
-        <v>7290718</v>
+        <v>7290605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125141702</v>
+        <v>124754557</v>
       </c>
       <c r="B17" t="n">
-        <v>74893</v>
+        <v>96979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782114</v>
+        <v>782122</v>
       </c>
       <c r="R17" t="n">
-        <v>7290605</v>
+        <v>7290733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125141688</v>
+        <v>124754560</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125141675</v>
+        <v>125141668</v>
       </c>
       <c r="B19" t="n">
-        <v>92318</v>
+        <v>79428</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782232</v>
+        <v>782209</v>
       </c>
       <c r="R19" t="n">
-        <v>7290364</v>
+        <v>7290451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125141668</v>
+        <v>124754581</v>
       </c>
       <c r="B20" t="n">
-        <v>79428</v>
+        <v>74893</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,34 +2542,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782209</v>
+        <v>782114</v>
       </c>
       <c r="R20" t="n">
-        <v>7290451</v>
+        <v>7290605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,6 +2613,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2734,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125141670</v>
+        <v>124754553</v>
       </c>
       <c r="B22" t="n">
-        <v>79428</v>
+        <v>92318</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2750,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2774,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782114</v>
+        <v>782232</v>
       </c>
       <c r="R22" t="n">
-        <v>7290605</v>
+        <v>7290364</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754542</v>
+        <v>124754577</v>
       </c>
       <c r="B3" t="n">
-        <v>90934</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782254</v>
+        <v>782578</v>
       </c>
       <c r="R3" t="n">
-        <v>7290430</v>
+        <v>7290125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754572</v>
+        <v>124754574</v>
       </c>
       <c r="B4" t="n">
         <v>78455</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Silverstubbe delvis nedbruden</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754577</v>
+        <v>124754571</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782578</v>
+        <v>782209</v>
       </c>
       <c r="R5" t="n">
-        <v>7290125</v>
+        <v>7290451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754571</v>
+        <v>124754542</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>90934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782209</v>
+        <v>782254</v>
       </c>
       <c r="R6" t="n">
-        <v>7290451</v>
+        <v>7290430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791549</v>
+        <v>124791544</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>92277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782377</v>
+        <v>782230</v>
       </c>
       <c r="R7" t="n">
-        <v>7290562</v>
+        <v>7290358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791540</v>
+        <v>124791552</v>
       </c>
       <c r="B8" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782565</v>
+        <v>782269</v>
       </c>
       <c r="R8" t="n">
-        <v>7290181</v>
+        <v>7290338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791552</v>
+        <v>124791540</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782269</v>
+        <v>782565</v>
       </c>
       <c r="R9" t="n">
-        <v>7290338</v>
+        <v>7290181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791544</v>
+        <v>124791549</v>
       </c>
       <c r="B11" t="n">
-        <v>92277</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6055</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782230</v>
+        <v>782377</v>
       </c>
       <c r="R11" t="n">
-        <v>7290358</v>
+        <v>7290562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125141687</v>
+        <v>124754553</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>92318</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782118</v>
+        <v>782232</v>
       </c>
       <c r="R12" t="n">
-        <v>7290718</v>
+        <v>7290364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124754568</v>
+        <v>124754567</v>
       </c>
       <c r="B13" t="n">
         <v>78546</v>
@@ -1845,7 +1850,7 @@
         <v>782118</v>
       </c>
       <c r="R13" t="n">
-        <v>7290721</v>
+        <v>7290718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125141672</v>
+        <v>125141670</v>
       </c>
       <c r="B14" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754564</v>
+        <v>125141668</v>
       </c>
       <c r="B15" t="n">
-        <v>92328</v>
+        <v>79428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782219</v>
+        <v>782209</v>
       </c>
       <c r="R15" t="n">
-        <v>7290375</v>
+        <v>7290451</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141670</v>
+        <v>125141682</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>92328</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782114</v>
+        <v>782219</v>
       </c>
       <c r="R16" t="n">
-        <v>7290605</v>
+        <v>7290375</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124754557</v>
+        <v>125141676</v>
       </c>
       <c r="B17" t="n">
         <v>96979</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124754560</v>
+        <v>124754568</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125141668</v>
+        <v>125141702</v>
       </c>
       <c r="B19" t="n">
-        <v>79428</v>
+        <v>74893</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782209</v>
+        <v>782114</v>
       </c>
       <c r="R19" t="n">
-        <v>7290451</v>
+        <v>7290605</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124754581</v>
+        <v>125141672</v>
       </c>
       <c r="B20" t="n">
-        <v>74893</v>
+        <v>79399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,27 +2542,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
@@ -2613,7 +2610,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2738,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124754553</v>
+        <v>124754560</v>
       </c>
       <c r="B22" t="n">
-        <v>92318</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3100</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782232</v>
+        <v>782118</v>
       </c>
       <c r="R22" t="n">
-        <v>7290364</v>
+        <v>7290721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,6 +2810,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791552</v>
+        <v>124791540</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782269</v>
+        <v>782565</v>
       </c>
       <c r="R8" t="n">
-        <v>7290338</v>
+        <v>7290181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791540</v>
+        <v>124791552</v>
       </c>
       <c r="B9" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782565</v>
+        <v>782269</v>
       </c>
       <c r="R9" t="n">
-        <v>7290181</v>
+        <v>7290338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124754568</v>
+        <v>125141688</v>
       </c>
       <c r="B18" t="n">
         <v>78546</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754577</v>
+        <v>124754571</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782578</v>
+        <v>782209</v>
       </c>
       <c r="R3" t="n">
-        <v>7290125</v>
+        <v>7290451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754574</v>
+        <v>124754577</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782121</v>
+        <v>782578</v>
       </c>
       <c r="R4" t="n">
-        <v>7290732</v>
+        <v>7290125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Silverstubbe delvis nedbruden</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754571</v>
+        <v>124754572</v>
       </c>
       <c r="B5" t="n">
         <v>78455</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782209</v>
+        <v>782121</v>
       </c>
       <c r="R5" t="n">
-        <v>7290451</v>
+        <v>7290732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791544</v>
+        <v>124791553</v>
       </c>
       <c r="B7" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782230</v>
+        <v>782220</v>
       </c>
       <c r="R7" t="n">
-        <v>7290358</v>
+        <v>7290373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791540</v>
+        <v>124791549</v>
       </c>
       <c r="B8" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782565</v>
+        <v>782377</v>
       </c>
       <c r="R8" t="n">
-        <v>7290181</v>
+        <v>7290562</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791553</v>
+        <v>124791540</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782220</v>
+        <v>782565</v>
       </c>
       <c r="R10" t="n">
-        <v>7290373</v>
+        <v>7290181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791549</v>
+        <v>124791544</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>92277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782377</v>
+        <v>782230</v>
       </c>
       <c r="R11" t="n">
-        <v>7290562</v>
+        <v>7290358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124754553</v>
+        <v>124754581</v>
       </c>
       <c r="B12" t="n">
-        <v>92318</v>
+        <v>74893</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,34 +1716,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782232</v>
+        <v>782114</v>
       </c>
       <c r="R12" t="n">
-        <v>7290364</v>
+        <v>7290605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,6 +1787,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1807,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124754567</v>
+        <v>125141676</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>96979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782118</v>
+        <v>782122</v>
       </c>
       <c r="R13" t="n">
-        <v>7290718</v>
+        <v>7290733</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1908,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125141670</v>
+        <v>125141668</v>
       </c>
       <c r="B14" t="n">
         <v>79428</v>
@@ -1949,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782114</v>
+        <v>782209</v>
       </c>
       <c r="R14" t="n">
-        <v>7290605</v>
+        <v>7290451</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125141668</v>
+        <v>125141688</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782209</v>
+        <v>782118</v>
       </c>
       <c r="R15" t="n">
-        <v>7290451</v>
+        <v>7290721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,6 +2086,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141682</v>
+        <v>125141672</v>
       </c>
       <c r="B16" t="n">
-        <v>92328</v>
+        <v>79399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2133,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782219</v>
+        <v>782114</v>
       </c>
       <c r="R16" t="n">
-        <v>7290375</v>
+        <v>7290605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125141676</v>
+        <v>124754553</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
+        <v>92318</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2231,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>3100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782122</v>
+        <v>782232</v>
       </c>
       <c r="R17" t="n">
-        <v>7290733</v>
+        <v>7290364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125141688</v>
+        <v>124754580</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>74893</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,34 +2337,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782118</v>
+        <v>782435</v>
       </c>
       <c r="R18" t="n">
-        <v>7290721</v>
+        <v>7290481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,17 +2402,13 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2424,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125141702</v>
+        <v>124754564</v>
       </c>
       <c r="B19" t="n">
-        <v>74893</v>
+        <v>92328</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2443,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782114</v>
+        <v>782219</v>
       </c>
       <c r="R19" t="n">
-        <v>7290605</v>
+        <v>7290375</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125141672</v>
+        <v>125141670</v>
       </c>
       <c r="B20" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124754580</v>
+        <v>124754567</v>
       </c>
       <c r="B21" t="n">
-        <v>74893</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,37 +2647,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782435</v>
+        <v>782118</v>
       </c>
       <c r="R21" t="n">
-        <v>7290481</v>
+        <v>7290718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754571</v>
+        <v>124754542</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>90934</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782209</v>
+        <v>782254</v>
       </c>
       <c r="R3" t="n">
-        <v>7290451</v>
+        <v>7290430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754542</v>
+        <v>124754571</v>
       </c>
       <c r="B6" t="n">
-        <v>90934</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782254</v>
+        <v>782209</v>
       </c>
       <c r="R6" t="n">
-        <v>7290430</v>
+        <v>7290451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791553</v>
+        <v>124791552</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782220</v>
+        <v>782269</v>
       </c>
       <c r="R7" t="n">
-        <v>7290373</v>
+        <v>7290338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791549</v>
+        <v>124791544</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>92277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782377</v>
+        <v>782230</v>
       </c>
       <c r="R8" t="n">
-        <v>7290562</v>
+        <v>7290358</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791552</v>
+        <v>124791553</v>
       </c>
       <c r="B9" t="n">
         <v>92293</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782269</v>
+        <v>782220</v>
       </c>
       <c r="R9" t="n">
-        <v>7290338</v>
+        <v>7290373</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791544</v>
+        <v>124791549</v>
       </c>
       <c r="B11" t="n">
-        <v>92277</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6055</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782230</v>
+        <v>782377</v>
       </c>
       <c r="R11" t="n">
-        <v>7290358</v>
+        <v>7290562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124754581</v>
+        <v>125141672</v>
       </c>
       <c r="B12" t="n">
-        <v>74893</v>
+        <v>79399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,27 +1716,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
@@ -1787,7 +1784,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1908,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125141668</v>
+        <v>124754568</v>
       </c>
       <c r="B14" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782209</v>
+        <v>782118</v>
       </c>
       <c r="R14" t="n">
-        <v>7290451</v>
+        <v>7290721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,6 +1980,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2010,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125141688</v>
+        <v>124754564</v>
       </c>
       <c r="B15" t="n">
-        <v>78546</v>
+        <v>92328</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782118</v>
+        <v>782219</v>
       </c>
       <c r="R15" t="n">
-        <v>7290721</v>
+        <v>7290375</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141672</v>
+        <v>124754581</v>
       </c>
       <c r="B16" t="n">
-        <v>79399</v>
+        <v>74893</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,24 +2129,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
@@ -2201,6 +2200,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124754564</v>
+        <v>125141668</v>
       </c>
       <c r="B19" t="n">
-        <v>92328</v>
+        <v>79428</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782219</v>
+        <v>782209</v>
       </c>
       <c r="R19" t="n">
-        <v>7290375</v>
+        <v>7290451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125141670</v>
+        <v>124754560</v>
       </c>
       <c r="B20" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R20" t="n">
-        <v>7290605</v>
+        <v>7290721</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,6 +2605,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2631,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124754567</v>
+        <v>125141670</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2647,21 +2652,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2671,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R21" t="n">
-        <v>7290718</v>
+        <v>7290605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124754560</v>
+        <v>124754567</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2776,7 +2781,7 @@
         <v>782118</v>
       </c>
       <c r="R22" t="n">
-        <v>7290721</v>
+        <v>7290718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2809,11 +2814,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754542</v>
+        <v>124754572</v>
       </c>
       <c r="B3" t="n">
-        <v>90934</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782254</v>
+        <v>782121</v>
       </c>
       <c r="R3" t="n">
-        <v>7290430</v>
+        <v>7290732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754572</v>
+        <v>124754571</v>
       </c>
       <c r="B5" t="n">
         <v>78455</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782121</v>
+        <v>782209</v>
       </c>
       <c r="R5" t="n">
-        <v>7290732</v>
+        <v>7290451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754571</v>
+        <v>124754542</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>90934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782209</v>
+        <v>782254</v>
       </c>
       <c r="R6" t="n">
-        <v>7290451</v>
+        <v>7290430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791552</v>
+        <v>124791540</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782269</v>
+        <v>782565</v>
       </c>
       <c r="R7" t="n">
-        <v>7290338</v>
+        <v>7290181</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791540</v>
+        <v>124791549</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782565</v>
+        <v>782377</v>
       </c>
       <c r="R10" t="n">
-        <v>7290181</v>
+        <v>7290562</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791549</v>
+        <v>124791552</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782377</v>
+        <v>782269</v>
       </c>
       <c r="R11" t="n">
-        <v>7290562</v>
+        <v>7290338</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125141672</v>
+        <v>125141687</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R12" t="n">
-        <v>7290605</v>
+        <v>7290718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125141676</v>
+        <v>125141670</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>79428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782122</v>
+        <v>782114</v>
       </c>
       <c r="R13" t="n">
-        <v>7290733</v>
+        <v>7290605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124754568</v>
+        <v>124754581</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>74893</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,34 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R14" t="n">
-        <v>7290721</v>
+        <v>7290605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,17 +1985,13 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2011,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754564</v>
+        <v>124754560</v>
       </c>
       <c r="B15" t="n">
-        <v>92328</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782219</v>
+        <v>782118</v>
       </c>
       <c r="R15" t="n">
-        <v>7290375</v>
+        <v>7290721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,6 +2086,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124754581</v>
+        <v>125141668</v>
       </c>
       <c r="B16" t="n">
-        <v>74893</v>
+        <v>79428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,37 +2133,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782114</v>
+        <v>782209</v>
       </c>
       <c r="R16" t="n">
-        <v>7290605</v>
+        <v>7290451</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,7 +2201,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124754553</v>
+        <v>125141682</v>
       </c>
       <c r="B17" t="n">
-        <v>92318</v>
+        <v>92328</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3100</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782232</v>
+        <v>782219</v>
       </c>
       <c r="R17" t="n">
-        <v>7290364</v>
+        <v>7290375</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124754580</v>
+        <v>124754557</v>
       </c>
       <c r="B18" t="n">
-        <v>74893</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,41 +2333,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782435</v>
+        <v>782122</v>
       </c>
       <c r="R18" t="n">
-        <v>7290481</v>
+        <v>7290733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,7 +2405,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125141668</v>
+        <v>124754568</v>
       </c>
       <c r="B19" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782209</v>
+        <v>782118</v>
       </c>
       <c r="R19" t="n">
-        <v>7290451</v>
+        <v>7290721</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,6 +2499,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124754560</v>
+        <v>124754580</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>74893</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,34 +2546,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782118</v>
+        <v>782435</v>
       </c>
       <c r="R20" t="n">
-        <v>7290721</v>
+        <v>7290481</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,17 +2611,13 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125141670</v>
+        <v>125141675</v>
       </c>
       <c r="B21" t="n">
-        <v>79428</v>
+        <v>92318</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782114</v>
+        <v>782232</v>
       </c>
       <c r="R21" t="n">
-        <v>7290605</v>
+        <v>7290364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124754567</v>
+        <v>125141672</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R22" t="n">
-        <v>7290718</v>
+        <v>7290605</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124754581</v>
+        <v>124754560</v>
       </c>
       <c r="B14" t="n">
-        <v>74893</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,37 +1920,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R14" t="n">
-        <v>7290605</v>
+        <v>7290721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,13 +1982,17 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754560</v>
+        <v>124754581</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>74893</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,34 +2027,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R15" t="n">
-        <v>7290721</v>
+        <v>7290605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,17 +2092,13 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754572</v>
+        <v>124754577</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782121</v>
+        <v>782578</v>
       </c>
       <c r="R3" t="n">
-        <v>7290732</v>
+        <v>7290125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754577</v>
+        <v>124754572</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782578</v>
+        <v>782121</v>
       </c>
       <c r="R4" t="n">
-        <v>7290125</v>
+        <v>7290732</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791540</v>
+        <v>124791544</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>92277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782565</v>
+        <v>782230</v>
       </c>
       <c r="R7" t="n">
-        <v>7290181</v>
+        <v>7290358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791544</v>
+        <v>124791553</v>
       </c>
       <c r="B8" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782230</v>
+        <v>782220</v>
       </c>
       <c r="R8" t="n">
-        <v>7290358</v>
+        <v>7290373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791553</v>
+        <v>124791540</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782220</v>
+        <v>782565</v>
       </c>
       <c r="R9" t="n">
-        <v>7290373</v>
+        <v>7290181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791549</v>
+        <v>124791552</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782377</v>
+        <v>782269</v>
       </c>
       <c r="R10" t="n">
-        <v>7290562</v>
+        <v>7290338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791552</v>
+        <v>124791549</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782269</v>
+        <v>782377</v>
       </c>
       <c r="R11" t="n">
-        <v>7290338</v>
+        <v>7290562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125141687</v>
+        <v>125141688</v>
       </c>
       <c r="B12" t="n">
         <v>78546</v>
@@ -1743,7 +1743,7 @@
         <v>782118</v>
       </c>
       <c r="R12" t="n">
-        <v>7290718</v>
+        <v>7290721</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125141670</v>
+        <v>125141682</v>
       </c>
       <c r="B13" t="n">
-        <v>79428</v>
+        <v>92328</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782114</v>
+        <v>782219</v>
       </c>
       <c r="R13" t="n">
-        <v>7290605</v>
+        <v>7290375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754581</v>
+        <v>125141702</v>
       </c>
       <c r="B15" t="n">
         <v>74893</v>
@@ -2045,9 +2050,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
@@ -2098,7 +2100,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2117,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141668</v>
+        <v>125141675</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>92318</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782209</v>
+        <v>782232</v>
       </c>
       <c r="R16" t="n">
-        <v>7290451</v>
+        <v>7290364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125141682</v>
+        <v>124754557</v>
       </c>
       <c r="B17" t="n">
-        <v>92328</v>
+        <v>96979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782219</v>
+        <v>782122</v>
       </c>
       <c r="R17" t="n">
-        <v>7290375</v>
+        <v>7290733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124754557</v>
+        <v>124754580</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>74893</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,38 +2334,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782122</v>
+        <v>782435</v>
       </c>
       <c r="R18" t="n">
-        <v>7290733</v>
+        <v>7290481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,6 +2409,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2423,7 +2428,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124754568</v>
+        <v>125141687</v>
       </c>
       <c r="B19" t="n">
         <v>78546</v>
@@ -2466,7 +2471,7 @@
         <v>782118</v>
       </c>
       <c r="R19" t="n">
-        <v>7290721</v>
+        <v>7290718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2499,11 +2504,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2530,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124754580</v>
+        <v>125141670</v>
       </c>
       <c r="B20" t="n">
-        <v>74893</v>
+        <v>79428</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,37 +2546,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782435</v>
+        <v>782114</v>
       </c>
       <c r="R20" t="n">
-        <v>7290481</v>
+        <v>7290605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,7 +2614,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2636,10 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125141675</v>
+        <v>125141668</v>
       </c>
       <c r="B21" t="n">
-        <v>92318</v>
+        <v>79428</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,21 +2648,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3100</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782232</v>
+        <v>782209</v>
       </c>
       <c r="R21" t="n">
-        <v>7290364</v>
+        <v>7290451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125141702</v>
+        <v>125141675</v>
       </c>
       <c r="B15" t="n">
-        <v>74893</v>
+        <v>92318</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>3100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782114</v>
+        <v>782232</v>
       </c>
       <c r="R15" t="n">
-        <v>7290605</v>
+        <v>7290364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141675</v>
+        <v>125141702</v>
       </c>
       <c r="B16" t="n">
-        <v>92318</v>
+        <v>74893</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3100</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782232</v>
+        <v>782114</v>
       </c>
       <c r="R16" t="n">
-        <v>7290364</v>
+        <v>7290605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754572</v>
+        <v>124754542</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>90934</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782121</v>
+        <v>782254</v>
       </c>
       <c r="R4" t="n">
-        <v>7290732</v>
+        <v>7290430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754571</v>
+        <v>124754574</v>
       </c>
       <c r="B5" t="n">
         <v>78455</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782209</v>
+        <v>782121</v>
       </c>
       <c r="R5" t="n">
-        <v>7290451</v>
+        <v>7290732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Silverstubbe delvis nedbruden</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754542</v>
+        <v>124754571</v>
       </c>
       <c r="B6" t="n">
-        <v>90934</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782254</v>
+        <v>782209</v>
       </c>
       <c r="R6" t="n">
-        <v>7290430</v>
+        <v>7290451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791544</v>
+        <v>124791552</v>
       </c>
       <c r="B7" t="n">
-        <v>92277</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782230</v>
+        <v>782269</v>
       </c>
       <c r="R7" t="n">
-        <v>7290358</v>
+        <v>7290338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791553</v>
+        <v>124791544</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>92277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782220</v>
+        <v>782230</v>
       </c>
       <c r="R8" t="n">
-        <v>7290373</v>
+        <v>7290358</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791540</v>
+        <v>124791553</v>
       </c>
       <c r="B9" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782565</v>
+        <v>782220</v>
       </c>
       <c r="R9" t="n">
-        <v>7290181</v>
+        <v>7290373</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791552</v>
+        <v>124791540</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782269</v>
+        <v>782565</v>
       </c>
       <c r="R10" t="n">
-        <v>7290338</v>
+        <v>7290181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125141688</v>
+        <v>125141670</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R12" t="n">
-        <v>7290721</v>
+        <v>7290605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125141682</v>
+        <v>124754581</v>
       </c>
       <c r="B13" t="n">
-        <v>92328</v>
+        <v>74893</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,34 +1823,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782219</v>
+        <v>782114</v>
       </c>
       <c r="R13" t="n">
-        <v>7290375</v>
+        <v>7290605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1894,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1909,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124754560</v>
+        <v>124754568</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2016,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125141675</v>
+        <v>124754560</v>
       </c>
       <c r="B15" t="n">
-        <v>92318</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2036,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3100</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782232</v>
+        <v>782118</v>
       </c>
       <c r="R15" t="n">
-        <v>7290364</v>
+        <v>7290721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,6 +2096,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141702</v>
+        <v>125141668</v>
       </c>
       <c r="B16" t="n">
-        <v>74893</v>
+        <v>79428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782114</v>
+        <v>782209</v>
       </c>
       <c r="R16" t="n">
-        <v>7290605</v>
+        <v>7290451</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124754557</v>
+        <v>125141672</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
+        <v>79399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2241,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782122</v>
+        <v>782114</v>
       </c>
       <c r="R17" t="n">
-        <v>7290733</v>
+        <v>7290605</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124754580</v>
+        <v>125141687</v>
       </c>
       <c r="B18" t="n">
-        <v>74893</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,37 +2347,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782435</v>
+        <v>782118</v>
       </c>
       <c r="R18" t="n">
-        <v>7290481</v>
+        <v>7290718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2415,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2428,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125141687</v>
+        <v>124754557</v>
       </c>
       <c r="B19" t="n">
-        <v>78546</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,25 +2445,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782118</v>
+        <v>782122</v>
       </c>
       <c r="R19" t="n">
-        <v>7290718</v>
+        <v>7290733</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125141670</v>
+        <v>125141682</v>
       </c>
       <c r="B20" t="n">
-        <v>79428</v>
+        <v>92328</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,21 +2551,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782114</v>
+        <v>782219</v>
       </c>
       <c r="R20" t="n">
-        <v>7290605</v>
+        <v>7290375</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125141668</v>
+        <v>124754580</v>
       </c>
       <c r="B21" t="n">
-        <v>79428</v>
+        <v>74893</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2648,34 +2653,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782209</v>
+        <v>782435</v>
       </c>
       <c r="R21" t="n">
-        <v>7290451</v>
+        <v>7290481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,6 +2724,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2734,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125141672</v>
+        <v>124754553</v>
       </c>
       <c r="B22" t="n">
-        <v>79399</v>
+        <v>92318</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2750,21 +2759,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2774,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782114</v>
+        <v>782232</v>
       </c>
       <c r="R22" t="n">
-        <v>7290605</v>
+        <v>7290364</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124633210</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754577</v>
+        <v>124754572</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782578</v>
+        <v>782121</v>
       </c>
       <c r="R3" t="n">
-        <v>7290125</v>
+        <v>7290732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754542</v>
+        <v>124754571</v>
       </c>
       <c r="B4" t="n">
-        <v>90934</v>
+        <v>78592</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782254</v>
+        <v>782209</v>
       </c>
       <c r="R4" t="n">
-        <v>7290430</v>
+        <v>7290451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754574</v>
+        <v>124754577</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>92448</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782121</v>
+        <v>782578</v>
       </c>
       <c r="R5" t="n">
-        <v>7290732</v>
+        <v>7290125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Silverstubbe delvis nedbruden</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754571</v>
+        <v>124754542</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>91088</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782209</v>
+        <v>782254</v>
       </c>
       <c r="R6" t="n">
-        <v>7290451</v>
+        <v>7290430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1188,7 @@
         <v>124791552</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791544</v>
+        <v>124791540</v>
       </c>
       <c r="B8" t="n">
-        <v>92277</v>
+        <v>79536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782230</v>
+        <v>782565</v>
       </c>
       <c r="R8" t="n">
-        <v>7290358</v>
+        <v>7290181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791553</v>
+        <v>124791544</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>92432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782220</v>
+        <v>782230</v>
       </c>
       <c r="R9" t="n">
-        <v>7290373</v>
+        <v>7290358</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791540</v>
+        <v>124791549</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782565</v>
+        <v>782377</v>
       </c>
       <c r="R10" t="n">
-        <v>7290181</v>
+        <v>7290562</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791549</v>
+        <v>124791553</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>92448</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782377</v>
+        <v>782220</v>
       </c>
       <c r="R11" t="n">
-        <v>7290562</v>
+        <v>7290373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125141670</v>
+        <v>124754567</v>
       </c>
       <c r="B12" t="n">
-        <v>79428</v>
+        <v>78683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R12" t="n">
-        <v>7290605</v>
+        <v>7290718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124754581</v>
+        <v>124754568</v>
       </c>
       <c r="B13" t="n">
-        <v>74893</v>
+        <v>78683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1818,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R13" t="n">
-        <v>7290605</v>
+        <v>7290721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,13 +1880,17 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1913,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124754568</v>
+        <v>125141676</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>97147</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782118</v>
+        <v>782122</v>
       </c>
       <c r="R14" t="n">
-        <v>7290721</v>
+        <v>7290733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754560</v>
+        <v>125141702</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>75017</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2060,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R15" t="n">
-        <v>7290721</v>
+        <v>7290605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141668</v>
+        <v>124754580</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>75017</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,34 +2129,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782209</v>
+        <v>782435</v>
       </c>
       <c r="R16" t="n">
-        <v>7290451</v>
+        <v>7290481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,6 +2200,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125141672</v>
+        <v>125141670</v>
       </c>
       <c r="B17" t="n">
-        <v>79399</v>
+        <v>79565</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2331,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125141687</v>
+        <v>124754553</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>92473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>3100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782118</v>
+        <v>782232</v>
       </c>
       <c r="R18" t="n">
-        <v>7290718</v>
+        <v>7290364</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124754557</v>
+        <v>125141668</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>79565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,25 +2435,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782122</v>
+        <v>782209</v>
       </c>
       <c r="R19" t="n">
-        <v>7290733</v>
+        <v>7290451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,7 +2528,7 @@
         <v>125141682</v>
       </c>
       <c r="B20" t="n">
-        <v>92328</v>
+        <v>92484</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124754580</v>
+        <v>124754560</v>
       </c>
       <c r="B21" t="n">
-        <v>74893</v>
+        <v>78684</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,37 +2643,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782435</v>
+        <v>782118</v>
       </c>
       <c r="R21" t="n">
-        <v>7290481</v>
+        <v>7290721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,13 +2705,17 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2743,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124754553</v>
+        <v>125141672</v>
       </c>
       <c r="B22" t="n">
-        <v>92318</v>
+        <v>79536</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2759,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3100</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782232</v>
+        <v>782114</v>
       </c>
       <c r="R22" t="n">
-        <v>7290364</v>
+        <v>7290605</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -2525,7 +2525,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125141682</v>
+        <v>124754564</v>
       </c>
       <c r="B20" t="n">
         <v>92484</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754572</v>
+        <v>124754574</v>
       </c>
       <c r="B3" t="n">
         <v>78592</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Silverstubbe delvis nedbruden</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754577</v>
+        <v>124754542</v>
       </c>
       <c r="B5" t="n">
-        <v>92448</v>
+        <v>91088</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782578</v>
+        <v>782254</v>
       </c>
       <c r="R5" t="n">
-        <v>7290125</v>
+        <v>7290430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754542</v>
+        <v>124754577</v>
       </c>
       <c r="B6" t="n">
-        <v>91088</v>
+        <v>92448</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782254</v>
+        <v>782578</v>
       </c>
       <c r="R6" t="n">
-        <v>7290430</v>
+        <v>7290125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791552</v>
+        <v>124791549</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782269</v>
+        <v>782377</v>
       </c>
       <c r="R7" t="n">
-        <v>7290338</v>
+        <v>7290562</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791540</v>
+        <v>124791552</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>92448</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782565</v>
+        <v>782269</v>
       </c>
       <c r="R8" t="n">
-        <v>7290181</v>
+        <v>7290338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791544</v>
+        <v>124791540</v>
       </c>
       <c r="B9" t="n">
-        <v>92432</v>
+        <v>79536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782230</v>
+        <v>782565</v>
       </c>
       <c r="R9" t="n">
-        <v>7290358</v>
+        <v>7290181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791549</v>
+        <v>124791544</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>92432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782377</v>
+        <v>782230</v>
       </c>
       <c r="R10" t="n">
-        <v>7290562</v>
+        <v>7290358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124754567</v>
+        <v>124754557</v>
       </c>
       <c r="B12" t="n">
-        <v>78683</v>
+        <v>97147</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782118</v>
+        <v>782122</v>
       </c>
       <c r="R12" t="n">
-        <v>7290718</v>
+        <v>7290733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124754568</v>
+        <v>125141675</v>
       </c>
       <c r="B13" t="n">
-        <v>78683</v>
+        <v>92473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782118</v>
+        <v>782232</v>
       </c>
       <c r="R13" t="n">
-        <v>7290721</v>
+        <v>7290364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125141676</v>
+        <v>124754568</v>
       </c>
       <c r="B14" t="n">
-        <v>97147</v>
+        <v>78683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782122</v>
+        <v>782118</v>
       </c>
       <c r="R14" t="n">
-        <v>7290733</v>
+        <v>7290721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1985,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125141702</v>
+        <v>124754560</v>
       </c>
       <c r="B15" t="n">
-        <v>75017</v>
+        <v>78684</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R15" t="n">
-        <v>7290605</v>
+        <v>7290721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,6 +2092,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124754580</v>
+        <v>124754581</v>
       </c>
       <c r="B16" t="n">
         <v>75017</v>
@@ -2156,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782435</v>
+        <v>782114</v>
       </c>
       <c r="R16" t="n">
-        <v>7290481</v>
+        <v>7290605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125141670</v>
+        <v>125141687</v>
       </c>
       <c r="B17" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2245,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R17" t="n">
-        <v>7290605</v>
+        <v>7290718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124754553</v>
+        <v>124754580</v>
       </c>
       <c r="B18" t="n">
-        <v>92473</v>
+        <v>75017</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,34 +2347,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3100</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782232</v>
+        <v>782435</v>
       </c>
       <c r="R18" t="n">
-        <v>7290364</v>
+        <v>7290481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,6 +2418,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2423,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125141668</v>
+        <v>124754564</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>92484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2453,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782209</v>
+        <v>782219</v>
       </c>
       <c r="R19" t="n">
-        <v>7290451</v>
+        <v>7290375</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124754564</v>
+        <v>125141668</v>
       </c>
       <c r="B20" t="n">
-        <v>92484</v>
+        <v>79565</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782219</v>
+        <v>782209</v>
       </c>
       <c r="R20" t="n">
-        <v>7290375</v>
+        <v>7290451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124754560</v>
+        <v>125141670</v>
       </c>
       <c r="B21" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R21" t="n">
-        <v>7290721</v>
+        <v>7290605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,11 +2717,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754560</v>
+        <v>124754581</v>
       </c>
       <c r="B15" t="n">
-        <v>78684</v>
+        <v>75017</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,34 +2032,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R15" t="n">
-        <v>7290721</v>
+        <v>7290605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,17 +2097,13 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2123,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124754581</v>
+        <v>124754560</v>
       </c>
       <c r="B16" t="n">
-        <v>75017</v>
+        <v>78684</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,37 +2138,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R16" t="n">
-        <v>7290605</v>
+        <v>7290721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,13 +2200,17 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -1705,37 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124754557</v>
+        <v>124754553</v>
       </c>
       <c r="B12" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782122</v>
+        <v>782232</v>
       </c>
       <c r="R12" t="n">
-        <v>7290733</v>
+        <v>7290364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,15 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125141675</v>
+        <v>124754580</v>
       </c>
       <c r="B13" t="n">
-        <v>92473</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75058</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,34 +1813,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782232</v>
+        <v>782435</v>
       </c>
       <c r="R13" t="n">
-        <v>7290364</v>
+        <v>7290481</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1884,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1909,15 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124754568</v>
+        <v>125141670</v>
       </c>
       <c r="B14" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1914,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782118</v>
+        <v>782114</v>
       </c>
       <c r="R14" t="n">
-        <v>7290721</v>
+        <v>7290605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,11 +1974,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,15 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124754581</v>
+        <v>125141702</v>
       </c>
       <c r="B15" t="n">
-        <v>75017</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,9 +2029,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
@@ -2103,7 +2079,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2122,15 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124754560</v>
+        <v>125141687</v>
       </c>
       <c r="B16" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,7 +2135,7 @@
         <v>782118</v>
       </c>
       <c r="R16" t="n">
-        <v>7290721</v>
+        <v>7290718</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2168,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,15 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125141687</v>
+        <v>124754564</v>
       </c>
       <c r="B17" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,21 +2205,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782118</v>
+        <v>782219</v>
       </c>
       <c r="R17" t="n">
-        <v>7290718</v>
+        <v>7290375</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,15 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124754580</v>
+        <v>125141672</v>
       </c>
       <c r="B18" t="n">
-        <v>75017</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,37 +2302,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782435</v>
+        <v>782114</v>
       </c>
       <c r="R18" t="n">
-        <v>7290481</v>
+        <v>7290605</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,7 +2370,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2437,15 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124754564</v>
+        <v>124754568</v>
       </c>
       <c r="B19" t="n">
-        <v>92484</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782219</v>
+        <v>782118</v>
       </c>
       <c r="R19" t="n">
-        <v>7290375</v>
+        <v>7290721</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2459,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,37 +2490,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125141668</v>
+        <v>124754557</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2525,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782209</v>
+        <v>782122</v>
       </c>
       <c r="R20" t="n">
-        <v>7290451</v>
+        <v>7290733</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,15 +2587,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125141670</v>
+        <v>124754560</v>
       </c>
       <c r="B21" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2657,21 +2598,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2622,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782114</v>
+        <v>782118</v>
       </c>
       <c r="R21" t="n">
-        <v>7290605</v>
+        <v>7290721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,6 +2658,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,15 +2689,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125141672</v>
+        <v>125141668</v>
       </c>
       <c r="B22" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,21 +2700,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782114</v>
+        <v>782209</v>
       </c>
       <c r="R22" t="n">
-        <v>7290605</v>
+        <v>7290451</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124633210</v>
+        <v>124754580</v>
       </c>
       <c r="B2" t="n">
-        <v>57053</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>782119</v>
+        <v>782435</v>
       </c>
       <c r="R2" t="n">
-        <v>7290637</v>
+        <v>7290481</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124754574</v>
+        <v>124754581</v>
       </c>
       <c r="B3" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>782121</v>
+        <v>782114</v>
       </c>
       <c r="R3" t="n">
-        <v>7290732</v>
+        <v>7290605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,17 +852,13 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Silverstubbe delvis nedbruden</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124754571</v>
+        <v>124633241</v>
       </c>
       <c r="B4" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>782209</v>
+        <v>782253</v>
       </c>
       <c r="R4" t="n">
-        <v>7290451</v>
+        <v>7290419</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124754542</v>
+        <v>124754571</v>
       </c>
       <c r="B5" t="n">
-        <v>91088</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>782254</v>
+        <v>782209</v>
       </c>
       <c r="R5" t="n">
-        <v>7290430</v>
+        <v>7290451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124754577</v>
+        <v>124754572</v>
       </c>
       <c r="B6" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>782578</v>
+        <v>782121</v>
       </c>
       <c r="R6" t="n">
-        <v>7290125</v>
+        <v>7290732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,50 +1168,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124791549</v>
+        <v>124633232</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>782377</v>
+        <v>782227</v>
       </c>
       <c r="R7" t="n">
-        <v>7290562</v>
+        <v>7290480</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1233,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,62 +1253,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124791552</v>
+        <v>124633237</v>
       </c>
       <c r="B8" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>782269</v>
+        <v>782438</v>
       </c>
       <c r="R8" t="n">
-        <v>7290338</v>
+        <v>7290695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1330,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,27 +1350,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124791540</v>
+        <v>124640980</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>782565</v>
+        <v>782427</v>
       </c>
       <c r="R9" t="n">
-        <v>7290181</v>
+        <v>7290743</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1427,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,50 +1459,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124791544</v>
+        <v>124754552</v>
       </c>
       <c r="B10" t="n">
-        <v>92432</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6055</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782230</v>
+        <v>782232</v>
       </c>
       <c r="R10" t="n">
-        <v>7290358</v>
+        <v>7290339</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,11 +1532,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1586,27 +1544,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124791553</v>
+        <v>124640986</v>
       </c>
       <c r="B11" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782220</v>
+        <v>782259</v>
       </c>
       <c r="R11" t="n">
-        <v>7290373</v>
+        <v>7290399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,12 +1621,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,7 +1656,7 @@
         <v>124754553</v>
       </c>
       <c r="B12" t="n">
-        <v>92527</v>
+        <v>93222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124754580</v>
+        <v>124754542</v>
       </c>
       <c r="B13" t="n">
-        <v>75058</v>
+        <v>91831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,37 +1761,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>782435</v>
+        <v>782254</v>
       </c>
       <c r="R13" t="n">
-        <v>7290481</v>
+        <v>7290430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1829,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1898,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125141670</v>
+        <v>118902943</v>
       </c>
       <c r="B14" t="n">
-        <v>79585</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1909,34 +1858,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>782114</v>
+        <v>782108</v>
       </c>
       <c r="R14" t="n">
-        <v>7290605</v>
+        <v>7290545</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,12 +1912,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1983,22 +1942,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125141702</v>
+        <v>118903340</v>
       </c>
       <c r="B15" t="n">
-        <v>75058</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2006,34 +1965,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>782114</v>
+        <v>782143</v>
       </c>
       <c r="R15" t="n">
-        <v>7290605</v>
+        <v>7290492</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,12 +2019,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125141687</v>
+        <v>124633244</v>
       </c>
       <c r="B16" t="n">
-        <v>78725</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>782118</v>
+        <v>782248</v>
       </c>
       <c r="R16" t="n">
-        <v>7290718</v>
+        <v>7290426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2157,12 +2126,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2189,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124754564</v>
+        <v>124640982</v>
       </c>
       <c r="B17" t="n">
-        <v>92538</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,34 +2169,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>782219</v>
+        <v>782231</v>
       </c>
       <c r="R17" t="n">
-        <v>7290375</v>
+        <v>7290433</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2254,12 +2223,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,22 +2243,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125141672</v>
+        <v>124640984</v>
       </c>
       <c r="B18" t="n">
-        <v>79556</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,34 +2266,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>782114</v>
+        <v>782201</v>
       </c>
       <c r="R18" t="n">
-        <v>7290605</v>
+        <v>7290462</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,12 +2320,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2371,22 +2340,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124754568</v>
+        <v>124640985</v>
       </c>
       <c r="B19" t="n">
-        <v>78725</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,34 +2363,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>782118</v>
+        <v>782289</v>
       </c>
       <c r="R19" t="n">
-        <v>7290721</v>
+        <v>7290359</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,17 +2417,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2473,44 +2437,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124754557</v>
+        <v>124754577</v>
       </c>
       <c r="B20" t="n">
-        <v>97202</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2484,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>782122</v>
+        <v>782578</v>
       </c>
       <c r="R20" t="n">
-        <v>7290733</v>
+        <v>7290125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,10 +2546,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124754560</v>
+        <v>124754579</v>
       </c>
       <c r="B21" t="n">
-        <v>78726</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,21 +2557,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>782118</v>
+        <v>782174</v>
       </c>
       <c r="R21" t="n">
-        <v>7290721</v>
+        <v>7290528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,11 +2617,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2684,10 +2643,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125141668</v>
+        <v>124791552</v>
       </c>
       <c r="B22" t="n">
-        <v>79585</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2695,34 +2654,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>782209</v>
+        <v>782269</v>
       </c>
       <c r="R22" t="n">
-        <v>7290451</v>
+        <v>7290338</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2769,15 +2728,4386 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124791553</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>782220</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7290373</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118909012</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4740</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sotriska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lactarius lignyotus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gängesmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>782108</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7290545</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124640954</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>782422</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7290746</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124754564</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>782219</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7290375</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124791544</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93181</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>782230</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7290358</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124633235</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>782226</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7290481</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124754565</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>782246</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7290419</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124754566</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>782169</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7290528</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124754567</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>782118</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7290718</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124754568</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>782118</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7290721</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124633208</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>782282</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7290386</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124633209</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>782110</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7290605</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124754546</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>782162</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7290539</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Silverstubbe delvis nedbruten</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124791537</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>782155</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7290552</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125141668</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>782209</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7290451</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125141670</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>782114</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7290605</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118904723</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gängesmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>782143</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7290492</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125061502</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>782402</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7290733</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124791543</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>782450</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7290515</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124633210</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>782119</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7290637</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124791551</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>782135</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7290637</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124754558</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>782163</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7290484</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>tömmning</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125060607</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>782418</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7290732</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125061503</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>782223</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7290430</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124640958</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>782338</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7290449</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118904060</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gängesmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>782143</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7290492</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>119416285</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>782416</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7290528</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124754569</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>782394</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7290494</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124754570</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>782395</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7290480</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124791547</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>782387</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7290599</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124791548</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>782384</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7290574</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124791549</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>782377</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7290562</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124633215</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>782074</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7290847</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124640962</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>782138</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7290753</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>124754557</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>782122</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7290733</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>118904523</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gängesmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>782143</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7290492</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>124633218</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>782284</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7290387</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124754560</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>782118</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7290721</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124754561</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>782174</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7290529</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>124791539</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>782511</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7290463</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>124791540</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>782565</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7290181</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125141672</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>782114</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7290605</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125141673</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>782137</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7290681</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124754554</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>782326</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7290301</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754580</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754581</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633241</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754571</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754572</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633232</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633237</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640980</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754552</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640986</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754553</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754542</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118902943</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118903340</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633244</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640982</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640984</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640985</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754577</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754579</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2737,6 +2842,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791552</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791553</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2931,6 +3046,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118909012</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3028,6 +3148,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640954</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3125,6 +3250,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754564</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3227,6 +3357,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791544</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3324,6 +3459,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633235</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3421,6 +3561,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754565</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3518,6 +3663,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754566</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3615,6 +3765,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754567</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3717,6 +3872,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754568</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3814,6 +3974,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633208</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3911,6 +4076,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633209</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754546</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4110,6 +4285,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791537</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4207,6 +4387,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125141668</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4304,6 +4489,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125141670</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4411,6 +4601,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118904723</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4513,6 +4708,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125061502</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4615,6 +4815,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791543</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4712,6 +4917,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633210</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4817,6 +5027,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791551</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4919,6 +5134,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754558</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5024,6 +5244,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125060607</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5129,6 +5354,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125061503</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5234,6 +5464,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640958</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5347,6 +5582,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118904060</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5444,6 +5684,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119416285</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5541,6 +5786,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754569</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5638,6 +5888,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754570</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5735,6 +5990,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791547</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5832,6 +6092,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791548</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5929,6 +6194,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791549</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6026,6 +6296,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633215</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6123,6 +6398,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124640962</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6220,6 +6500,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754557</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6327,6 +6612,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118904523</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6424,6 +6714,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124633218</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6526,6 +6821,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754560</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6623,6 +6923,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754561</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6720,6 +7025,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791539</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6817,6 +7127,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124791540</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6914,6 +7229,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125141672</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7011,6 +7331,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125141673</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7108,8 +7433,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124754554</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>